--- a/data/trans_orig/P1804_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1804_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53852</t>
+          <t>55671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81672</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261517</t>
+          <t>262748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279600</t>
+          <t>279565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234851</t>
+          <t>233032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259471</t>
+          <t>258524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500792</t>
+          <t>505251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533427</t>
+          <t>534224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48885</t>
+          <t>45773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73808</t>
+          <t>73228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468390</t>
+          <t>466721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488188</t>
+          <t>487731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474199</t>
+          <t>477311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498776</t>
+          <t>500067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951851</t>
+          <t>952431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982495</t>
+          <t>983266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305032</t>
+          <t>304269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315098</t>
+          <t>315172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313297</t>
+          <t>311776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328166</t>
+          <t>328450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621671</t>
+          <t>622058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640207</t>
+          <t>640385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63182</t>
+          <t>64351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95526</t>
+          <t>95564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96107</t>
+          <t>95111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131452</t>
+          <t>132582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169438</t>
+          <t>167107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219962</t>
+          <t>217368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274438</t>
+          <t>274400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>305613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255831</t>
+          <t>254701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291176</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537285</t>
+          <t>539879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>587809</t>
+          <t>590140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197935</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208383</t>
+          <t>208309</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199466</t>
+          <t>199599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213266</t>
+          <t>213451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>402526</t>
+          <t>402376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419998</t>
+          <t>418966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258761</t>
+          <t>258033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270272</t>
+          <t>269738</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520498</t>
+          <t>521912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533391</t>
+          <t>533437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>43550</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>64179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64123</t>
+          <t>62875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100025</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611950</t>
+          <t>613008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634292</t>
+          <t>635350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626736</t>
+          <t>627115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654976</t>
+          <t>655433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1247827</t>
+          <t>1248576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1283729</t>
+          <t>1284977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>58301</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62677</t>
+          <t>64122</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101282</t>
+          <t>101847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104212</t>
+          <t>105504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149828</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>718629</t>
+          <t>720282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>744954</t>
+          <t>745186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724885</t>
+          <t>724320</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763490</t>
+          <t>762045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1454922</t>
+          <t>1453570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1500538</t>
+          <t>1499246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>186939</t>
+          <t>184751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>246481</t>
+          <t>243225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>322187</t>
+          <t>312856</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>391829</t>
+          <t>388852</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>520169</t>
+          <t>515476</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>614524</t>
+          <t>615517</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3147869</t>
+          <t>3151125</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3207411</t>
+          <t>3209599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3152713</t>
+          <t>3155690</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3222355</t>
+          <t>3231686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6324368</t>
+          <t>6323375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6418723</t>
+          <t>6423416</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306711</t>
+          <t>314671</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299092</t>
+          <t>309481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309817</t>
+          <t>317487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>279152</t>
+          <t>301422</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273898</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283231</t>
+          <t>305927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>585863</t>
+          <t>616092</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577941</t>
+          <t>607373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591124</t>
+          <t>621845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4417,42 +4417,42 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10592</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19591</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9270</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4613</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18757</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4505,67 +4505,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>516414</t>
+          <t>528735</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>508320</t>
+          <t>519100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>534621</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>525622</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>540128</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>98,06%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>504455</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>494968</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>509112</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1020869</t>
+          <t>1063356</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009782</t>
+          <t>1052041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026915</t>
+          <t>1069629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>38435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>304265</t>
+          <t>304490</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296496</t>
+          <t>297322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309096</t>
+          <t>309069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>321283</t>
+          <t>327754</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311009</t>
+          <t>317407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329076</t>
+          <t>335065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,17 +4918,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>625549</t>
+          <t>632245</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613325</t>
+          <t>620647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635446</t>
+          <t>641645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>106275</t>
+          <t>128069</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86804</t>
+          <t>105956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128327</t>
+          <t>155811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>124638</t>
+          <t>143629</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>125574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>163350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>230912</t>
+          <t>271698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167287</t>
+          <t>243541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274305</t>
+          <t>303057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>206282</t>
+          <t>245076</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184230</t>
+          <t>217334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>225753</t>
+          <t>267189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>351080</t>
+          <t>278332</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313392</t>
+          <t>258611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395158</t>
+          <t>296387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>557362</t>
+          <t>523409</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>513969</t>
+          <t>492050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620987</t>
+          <t>551566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176815</t>
+          <t>203577</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>200105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178143</t>
+          <t>205042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>204981</t>
+          <t>223372</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201953</t>
+          <t>219429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206835</t>
+          <t>225398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>381796</t>
+          <t>426949</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377619</t>
+          <t>422494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384485</t>
+          <t>429840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30968</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31423</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>252683</t>
+          <t>254227</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244287</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258849</t>
+          <t>259638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>234114</t>
+          <t>238719</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226088</t>
+          <t>229574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240773</t>
+          <t>245564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>486798</t>
+          <t>492946</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>475074</t>
+          <t>482419</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495269</t>
+          <t>501800</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>28749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49334</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>70383</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85164</t>
+          <t>85725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>94460</t>
+          <t>110868</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60401</t>
+          <t>92091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119458</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>589569</t>
+          <t>679203</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574945</t>
+          <t>661606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599929</t>
+          <t>690938</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>786962</t>
+          <t>696131</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761548</t>
+          <t>680789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818288</t>
+          <t>709850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1376532</t>
+          <t>1375333</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1351534</t>
+          <t>1352285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1410591</t>
+          <t>1394110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846712</t>
+          <t>766514</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846712</t>
+          <t>766514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846712</t>
+          <t>766514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470992</t>
+          <t>1486201</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470992</t>
+          <t>1486201</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470992</t>
+          <t>1486201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>30387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>916243</t>
+          <t>784215</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907268</t>
+          <t>774803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923643</t>
+          <t>790685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,17 +6598,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>809703</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690306</t>
+          <t>800944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704891</t>
+          <t>817181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1615344</t>
+          <t>1593917</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1601706</t>
+          <t>1579877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1628382</t>
+          <t>1604098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152011</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>226927</t>
+          <t>258774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228617</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>315698</t>
+          <t>351492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>403907</t>
+          <t>491092</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>519745</t>
+          <t>584145</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3268983</t>
+          <t>3314195</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3232890</t>
+          <t>3273988</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3307806</t>
+          <t>3343730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3381129</t>
+          <t>3410056</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3342160</t>
+          <t>3376397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3429241</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6650112</t>
+          <t>6724251</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6597930</t>
+          <t>6676506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6713768</t>
+          <t>6769559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
